--- a/Design-Files/TYPE-C_4K_RECEIVER-v1.0/BOM/CLIENT BOM - TYPEC_4KRECEIVER-v1.0.xlsx
+++ b/Design-Files/TYPE-C_4K_RECEIVER-v1.0/BOM/CLIENT BOM - TYPEC_4KRECEIVER-v1.0.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eSpark Cons Group\Documents\GitHub\Melih-SoundSensor\aaronsushinsky-wirelesshdmi-hw\Design-Files\TYPE-C_4K_RECEIVER-v1.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\aaronsushinsky-wirelesshdmi-hw\Design-Files\TYPE-C_4K_RECEIVER-v1.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FCF3D8-EAC7-44FD-8F98-7F8606FD94C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="478">
   <si>
     <t>#</t>
   </si>
@@ -88,19 +87,19 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C13, C14, C15, C16, C18, C19, C20, C21, C22, C23, C24, C25, C26, C31, C32, C40, C42, C43, C52, C77, C119, C120, C122, C132, C165, C173, C204, C205</t>
-  </si>
-  <si>
-    <t>C2, C10, C44, C51, C53, C56, C57, C58, C59, C60, C72, C80, C86, C141, C175, C176, C189, C293</t>
-  </si>
-  <si>
-    <t>C3, C38, C67, C106, C202, C256</t>
-  </si>
-  <si>
-    <t>C4, C33, C36, C37, C78, C138, C148, C164, C166, C178, C179, C188, C190, C192, C193, C194, C195, C203, C206, C207, C208, C209, C210, C211, C212, C213, C214, C215, C217, C218, C220, C221, C223, C225, C227, C228, C229, C232, C233, C234, C235, C236, C237, C240, C241, C242, C243, C244, C245, C246, C247, C248, C249, C250, C251, C257, C300</t>
-  </si>
-  <si>
-    <t>C5, C17, C84, C91, C92, C93, C96, C114, C115, C117, C134, C139, C142, C167, C191, C253, C262, C324</t>
+    <t>C1, C52</t>
+  </si>
+  <si>
+    <t>C2, C10, C53, C56, C57, C58, C59, C80, C86, C141, C175, C176, C189</t>
+  </si>
+  <si>
+    <t>C3, C38, C202, C256</t>
+  </si>
+  <si>
+    <t>C4, C33, C36, C37, C78, C148, C178, C179, C188, C190, C192, C193, C194, C195, C203, C206, C207, C208, C209, C210, C211, C212, C213, C214, C215, C217, C218, C220, C221, C223, C225, C227, C228, C229, C232, C233, C234, C235, C236, C237, C240, C241, C242, C243, C244, C245, C246, C247, C248, C249, C250, C251, C257, C300</t>
+  </si>
+  <si>
+    <t>C5, C17, C84, C91, C92, C93, C96, C114, C115, C117, C134, C167, C191, C253, C262, C324</t>
   </si>
   <si>
     <t>C6, C7</t>
@@ -115,7 +114,10 @@
     <t>C11</t>
   </si>
   <si>
-    <t>C12, C28, C46, C47, C48, C61, C62, C65, C69, C71, C85, C94, C95, C97, C98, C99, C100, C101, C102, C103, C186, C197, C198, C255, C287</t>
+    <t>C12, C28, C46, C47, C48, C61, C62, C65, C69, C71, C94, C95, C97, C98, C99, C100, C101, C102, C103, C186, C197, C198, C255, C287</t>
+  </si>
+  <si>
+    <t>C13, C14, C15, C16, C18, C19, C20, C21, C22, C23, C24, C25, C26, C31, C32, C40, C42, C43, C77, C119, C120, C122, C132, C165, C173, C204, C205</t>
   </si>
   <si>
     <t>C27, C29, C30, C63, C64, C68, C70, C73, C104, C105, C116, C196, C199, C200, C201, C230, C231, C290</t>
@@ -127,28 +129,46 @@
     <t>C39, C41, C252</t>
   </si>
   <si>
+    <t>C44, C51, C60, C72, C293</t>
+  </si>
+  <si>
     <t>C54, C55, C83, C87, C88, C89, C90, C107, C108, C109, C110, C111, C112, C113, C118, C123, C124, C125, C126, C127, C128, C131, C133, C135, C136, C137, C140, C143, C144, C145, C146, C147, C150, C151, C152, C153, C154, C155, C160, C161, C162, C163, C168, C170, C171, C172, C180, C181, C216, C239, C258, C310, C312, C313, C314, C315, C316, C317, C318, C319, C320, C321, C325, C326</t>
   </si>
   <si>
     <t>C66</t>
   </si>
   <si>
+    <t>C67, C106</t>
+  </si>
+  <si>
     <t>C82</t>
   </si>
   <si>
+    <t>C85</t>
+  </si>
+  <si>
     <t>C121, C149, C169, C174</t>
   </si>
   <si>
     <t>C129, C130</t>
   </si>
   <si>
+    <t>C138</t>
+  </si>
+  <si>
+    <t>C139, C142</t>
+  </si>
+  <si>
     <t>C156, C157, C158, C159</t>
   </si>
   <si>
+    <t>C164, C166</t>
+  </si>
+  <si>
     <t>C182, C183, C184, C185</t>
   </si>
   <si>
-    <t>C238, C292</t>
+    <t>C238</t>
   </si>
   <si>
     <t>C254</t>
@@ -157,6 +177,9 @@
     <t>C273, C275</t>
   </si>
   <si>
+    <t>C292</t>
+  </si>
+  <si>
     <t>C322, C323</t>
   </si>
   <si>
@@ -217,10 +240,10 @@
     <t>Q7, Q8</t>
   </si>
   <si>
-    <t>R1, R17, R33, R34, R41, R89, R105, R106, R107, R109, R110</t>
-  </si>
-  <si>
-    <t>R2, R28, R51, R95, R153</t>
+    <t>R1, R17, R34, R41, R89, R105, R106, R107, R109, R110</t>
+  </si>
+  <si>
+    <t>R2, R95</t>
   </si>
   <si>
     <t>R3, R29, R45, R50, R56, R87, R93, R114, R115, R116, R117, R126, R140, R169, R170, R171, R172, R173, R174, R175, R176</t>
@@ -229,7 +252,7 @@
     <t>R4, R27, R99, R123</t>
   </si>
   <si>
-    <t>R5, R42, R86, R94, R101, R132, R152</t>
+    <t>R5, R42, R86, R94, R132, R152</t>
   </si>
   <si>
     <t>R6, R7</t>
@@ -274,13 +297,19 @@
     <t>R25, R108</t>
   </si>
   <si>
+    <t>R28</t>
+  </si>
+  <si>
     <t>R30</t>
   </si>
   <si>
     <t>R32</t>
   </si>
   <si>
-    <t>R35, R36, R48, R49, R52, R54, R55, R74, R111, R112, R119, R122, R124, R125, R128, R130, R133, R134, R141, R142, R143, R144, R145, R146, R147, R148</t>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>R35, R36, R48, R49, R52, R54, R55, R74, R124, R125, R128, R130, R133, R134, R141, R142, R143, R144, R145, R146, R147</t>
   </si>
   <si>
     <t>R38</t>
@@ -295,6 +324,9 @@
     <t>R47, R85</t>
   </si>
   <si>
+    <t>R51</t>
+  </si>
+  <si>
     <t>R57, R69, R70, R80, R81</t>
   </si>
   <si>
@@ -313,12 +345,18 @@
     <t>R100</t>
   </si>
   <si>
+    <t>R101</t>
+  </si>
+  <si>
     <t>R102, R103</t>
   </si>
   <si>
     <t>R104</t>
   </si>
   <si>
+    <t>R111, R112, R119, R122</t>
+  </si>
+  <si>
     <t>R113, R118</t>
   </si>
   <si>
@@ -328,6 +366,12 @@
     <t>R135, R136, R137, R138, R139</t>
   </si>
   <si>
+    <t>R148</t>
+  </si>
+  <si>
+    <t>R153</t>
+  </si>
+  <si>
     <t>SW1, SW2, SW3</t>
   </si>
   <si>
@@ -391,19 +435,19 @@
     <t>Description</t>
   </si>
   <si>
-    <t>CAP CER 1UF 16V X5R 0402, CAP CER 1UF 10V X5R 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 0.1UF 16V X5R 0402, CAP CER 0.1UF 10V X5R 0402</t>
+    <t>CAP CER 1UF 16V X5R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 16V X5R 0402</t>
   </si>
   <si>
     <t>CAP CER 10UF 10V X5R 0402</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 10V X5R 0402, CAP CER 0.1UF 16V X7R 0402, CAP CER 0.1UF 50V X7R 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 4.7UF 10V X5R 0402, CAP CER 4.7UF 6.3V X5R 0402</t>
+    <t>CAP CER 0.1UF 10V X5R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 10V X5R 0402</t>
   </si>
   <si>
     <t>CAP CER 10PF 25V C0G 0201</t>
@@ -418,7 +462,10 @@
     <t>CAP CER 4700PF 50V X7R 0402</t>
   </si>
   <si>
-    <t>CAP CER 22UF 10V X5R 0603, 16V 22uF X5R ±20% 0603 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+    <t>CAP CER 22UF 10V X5R 0603</t>
+  </si>
+  <si>
+    <t>CAP CER 1UF 10V X5R 0402</t>
   </si>
   <si>
     <t>CAP CER 10UF 10V X5R 0603</t>
@@ -439,19 +486,31 @@
     <t>CAP CER 0.1UF 50V X5R 0603</t>
   </si>
   <si>
+    <t>16V 22uF X5R ±20% 0603 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+  </si>
+  <si>
     <t>CAP CER 1UF 10V X5R 0201</t>
   </si>
   <si>
     <t>CAP CER 18PF 50V C0G/NP0 0402</t>
   </si>
   <si>
+    <t>CAP CER 0.1UF 16V X7R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 6.3V X5R 0402</t>
+  </si>
+  <si>
     <t>50V 1nF X7R ±10% 0201 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
   </si>
   <si>
+    <t>CAP CER 0.1UF 50V X7R 0402</t>
+  </si>
+  <si>
     <t>CAP CER 15PF 50V C0G/NPO 0201</t>
   </si>
   <si>
-    <t>CAP CER 1000PF 50V C0G/NP0 0402, CAP CER 6.8PF 50V C0G/NPO 0402</t>
+    <t>CAP CER 1000PF 50V C0G/NP0 0402</t>
   </si>
   <si>
     <t>CAP CER 100PF 50V C0G/NP0 0402</t>
@@ -460,6 +519,9 @@
     <t>CAP CER 12PF 50V C0G/NP0 0402</t>
   </si>
   <si>
+    <t>CAP CER 6.8PF 50V C0G/NPO 0402</t>
+  </si>
+  <si>
     <t>CAP CER 15PF 50V C0G/NPO 0402</t>
   </si>
   <si>
@@ -520,10 +582,10 @@
     <t>Small Signal Bipolar Transistor, 0.6A I(C), 40V V(BR)CEO, 1-Element, NPN, Silicon</t>
   </si>
   <si>
-    <t>RES 10K OHM 1% 1/16W 0402, RES SMD 10K OHM 0.5% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RES 22 OHM 1% 1/16W 0402, RES 0 OHM JUMPER 1/16W 0402, RES 10K OHM 1% 1/16W 0402, RES 100K OHM 1% 1/16W 0402</t>
+    <t>RES 10K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 22 OHM 1% 1/16W 0402</t>
   </si>
   <si>
     <t>RES 0 OHM JUMPER 1/16W 0402</t>
@@ -532,7 +594,7 @@
     <t>RES 20K OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>RES 100K OHM 1% 1/16W 0402, RES SMD 100K OHM 0.1% 1/16W 0402</t>
+    <t>RES 100K OHM 1% 1/16W 0402</t>
   </si>
   <si>
     <t>RES SMD 2.2K OHM 1% 1/16W 0402</t>
@@ -553,9 +615,6 @@
     <t>RES 51K OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>RES 22 OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
     <t>RES 100 OHM Thick Film 0201 1% 1/20W ±200ppm/°C Molded SMD SMD Paper T/R</t>
   </si>
   <si>
@@ -583,7 +642,7 @@
     <t>RES SMD 31.6KOHM 0.5% 1/16W 0402</t>
   </si>
   <si>
-    <t>RES SMD 0 OHM JUMPER 1/20W 0201, RES SMD 10K OHM 1% 1/20W 0201, RES 1K OHM 1% 1/20W 0201</t>
+    <t>RES SMD 10K OHM 0.5% 1/16W 0402</t>
   </si>
   <si>
     <t>RES 120 OHM 1% 1/16W 0402</t>
@@ -613,6 +672,9 @@
     <t>RES 2K OHM 1% 1/16W 0402</t>
   </si>
   <si>
+    <t>RES SMD 100K OHM 0.1% 1/16W 0402</t>
+  </si>
+  <si>
     <t>RES 240 OHM 1% 1/16W 0402</t>
   </si>
   <si>
@@ -625,6 +687,9 @@
     <t>RES 30K OHM 1% 1/16W 0402</t>
   </si>
   <si>
+    <t>RES 1K OHM 1% 1/20W 0201</t>
+  </si>
+  <si>
     <t>SWITCH TACTILE SPST-NO 0.05A 12V</t>
   </si>
   <si>
@@ -715,30 +780,15 @@
     <t>IND-0603 (1608 Metric)</t>
   </si>
   <si>
-    <t>10118192-0001LF_</t>
-  </si>
-  <si>
-    <t>U.FL-R-SMT-1(80)_</t>
-  </si>
-  <si>
     <t>HDMI-101W</t>
   </si>
   <si>
     <t>GT-USB-8013A</t>
   </si>
   <si>
-    <t>Inductor 1008</t>
-  </si>
-  <si>
-    <t>WPN252012HR24MT_</t>
-  </si>
-  <si>
     <t>IND-0806</t>
   </si>
   <si>
-    <t>WPN4020H2R2MT_</t>
-  </si>
-  <si>
     <t>SWPA3015S2R2MT</t>
   </si>
   <si>
@@ -763,9 +813,6 @@
     <t>B3U-1000P</t>
   </si>
   <si>
-    <t>EVQPUA02K</t>
-  </si>
-  <si>
     <t>BGA-565(15.5x14.4)</t>
   </si>
   <si>
@@ -802,12 +849,6 @@
     <t>SMD3215-2P</t>
   </si>
   <si>
-    <t>X322524MOB4SI-</t>
-  </si>
-  <si>
-    <t>Q22FA12800078_</t>
-  </si>
-  <si>
     <t>SMD3225-4P</t>
   </si>
   <si>
@@ -817,19 +858,19 @@
     <t>Manufacturer Part Number</t>
   </si>
   <si>
-    <t>CC0402KRX5R7BB105, CC0402KRX5R6BB105</t>
-  </si>
-  <si>
-    <t>CC0402KRX5R7BB104, CC0402KRX5R6BB104</t>
-  </si>
-  <si>
-    <t>CC0402MRX5R6BB106, CL05A106MP5NUNC</t>
-  </si>
-  <si>
-    <t>CC0402KRX5R6BB104, CC0402JRX7R7BB104, GRM155R71H104ME14D</t>
-  </si>
-  <si>
-    <t>CC0402KRX5R6BB475, CC0402KRX5R5BB475</t>
+    <t>CC0402KRX5R7BB105</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R7BB104</t>
+  </si>
+  <si>
+    <t>CC0402MRX5R6BB106</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R6BB104</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R6BB475</t>
   </si>
   <si>
     <t>CGA1A2C0G1E100D030BA</t>
@@ -844,7 +885,10 @@
     <t>CC0402KRX7R9BB472</t>
   </si>
   <si>
-    <t>CC0603MRX5R6BB226, HGC0603R5226M160NTHJ</t>
+    <t>CC0603MRX5R6BB226</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R6BB105</t>
   </si>
   <si>
     <t>CC0603KRX5R6BB106</t>
@@ -862,22 +906,37 @@
     <t>GRM158R61A226ME15D</t>
   </si>
   <si>
+    <t>CL05A106MP5NUNC</t>
+  </si>
+  <si>
     <t>CC0603KRX5R9BB104</t>
   </si>
   <si>
+    <t>HGC0603R5226M160NTHJ</t>
+  </si>
+  <si>
     <t>CC0201MRX5R6BB105</t>
   </si>
   <si>
     <t>GCM1555C1H180GA16D</t>
   </si>
   <si>
+    <t>CC0402JRX7R7BB104</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R5BB475</t>
+  </si>
+  <si>
     <t>0201B102K500NT</t>
   </si>
   <si>
+    <t>GRM155R71H104ME14D</t>
+  </si>
+  <si>
     <t>CC0201JRNPO9BN150</t>
   </si>
   <si>
-    <t>GRM1555C1H102JA01D, CC0402CRNPO9BN6R8</t>
+    <t>GRM1555C1H102JA01D</t>
   </si>
   <si>
     <t>GRM1555C1H101JA01D</t>
@@ -886,6 +945,9 @@
     <t>GJM1555C1H120GB01D</t>
   </si>
   <si>
+    <t>CC0402CRNPO9BN6R8</t>
+  </si>
+  <si>
     <t>CQ0402GRNPO9BN150</t>
   </si>
   <si>
@@ -928,10 +990,10 @@
     <t>WPN4020H2R2MT</t>
   </si>
   <si>
-    <t>RC0402FR-0710KL, RE0402DRE0710KL</t>
-  </si>
-  <si>
-    <t>RC0402FR-0722RL, RC0402FR-070RL, RC0402FR-0710KL, RC0402FR-07100KL</t>
+    <t>RC0402FR-0710KL</t>
+  </si>
+  <si>
+    <t>RC0402FR-0722RL</t>
   </si>
   <si>
     <t>RC0402FR-070RL</t>
@@ -940,7 +1002,7 @@
     <t>RC0402FR-0720KL</t>
   </si>
   <si>
-    <t>RC0402FR-07100KL, RT0402BRD07100KL</t>
+    <t>RC0402FR-07100KL</t>
   </si>
   <si>
     <t>RC0402FR-072K2L</t>
@@ -961,9 +1023,6 @@
     <t>RC0402FR-0751KL</t>
   </si>
   <si>
-    <t>RC0402FR-0722RL</t>
-  </si>
-  <si>
     <t>RC0201FR-07100RL</t>
   </si>
   <si>
@@ -991,7 +1050,7 @@
     <t>RT0402DRE0731K6L</t>
   </si>
   <si>
-    <t>RC0201JR-070RL, RC0201FR-0710KL, RC0201FR-071KP</t>
+    <t>RE0402DRE0710KL</t>
   </si>
   <si>
     <t>RC0402FR-07120RL</t>
@@ -1021,6 +1080,9 @@
     <t>RC0402FR-072KL</t>
   </si>
   <si>
+    <t>RT0402BRD07100KL</t>
+  </si>
+  <si>
     <t>RC0402FR-07240RL</t>
   </si>
   <si>
@@ -1033,6 +1095,9 @@
     <t>RC0402FR-0730KL</t>
   </si>
   <si>
+    <t>RC0201FR-071KP</t>
+  </si>
+  <si>
     <t>EVQ-PUA02K</t>
   </si>
   <si>
@@ -1096,12 +1161,6 @@
     <t>Yageo</t>
   </si>
   <si>
-    <t>Yageo, Samsung</t>
-  </si>
-  <si>
-    <t>Yageo, Murata</t>
-  </si>
-  <si>
     <t>TDK</t>
   </si>
   <si>
@@ -1111,15 +1170,12 @@
     <t>Samsung</t>
   </si>
   <si>
-    <t>Yageo, Chinocera</t>
+    <t>Chinocera</t>
   </si>
   <si>
     <t>FH</t>
   </si>
   <si>
-    <t>Murata, Yageo</t>
-  </si>
-  <si>
     <t>TECH PUBLIC</t>
   </si>
   <si>
@@ -1204,9 +1260,6 @@
     <t>NDK</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>1uF</t>
   </si>
   <si>
@@ -1372,14 +1425,41 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Transistor</t>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Mosfet</t>
+  </si>
+  <si>
+    <t>DO NOT PLACE</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>1.5 3dBi Vertical 50W Antennas ROHS</t>
+  </si>
+  <si>
+    <t>BW258FNX50-9B1</t>
+  </si>
+  <si>
+    <t>BAT WIRELESS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1418,6 +1498,23 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1538,7 +1635,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1577,6 +1674,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1863,23 +1975,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1890,8 +2003,9 @@
       <c r="H1" s="2"/>
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="14"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -1903,25 +2017,28 @@
         <v>21</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>394</v>
+        <v>469</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>467</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="11">
         <f>ROW(B3) - ROW($B$2)</f>
@@ -1934,28 +2051,29 @@
         <v>22</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="J3" s="7">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B102" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B116" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -1965,25 +2083,26 @@
         <v>23</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="J4" s="9">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
@@ -1996,25 +2115,26 @@
         <v>24</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="J5" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" spans="1:11" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -2027,56 +2147,58 @@
         <v>25</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="J6" s="9">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="11">
         <f>ROW(B7) - ROW($B$2)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="J7" s="7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
@@ -2089,25 +2211,26 @@
         <v>27</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="J8" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="11">
         <f>ROW(B9) - ROW($B$2)</f>
@@ -2120,25 +2243,26 @@
         <v>28</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="J9" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
@@ -2151,25 +2275,26 @@
         <v>29</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="J10" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="9"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="11">
         <f>ROW(B11) - ROW($B$2)</f>
@@ -2182,25 +2307,26 @@
         <v>30</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="J11" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="11">
         <f t="shared" si="0"/>
@@ -2213,25 +2339,26 @@
         <v>31</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="J12" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="K12" s="9"/>
+    </row>
+    <row r="13" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="11">
         <f>ROW(B13) - ROW($B$2)</f>
@@ -2244,25 +2371,26 @@
         <v>32</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="J13" s="7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="11">
         <f t="shared" si="0"/>
@@ -2275,25 +2403,26 @@
         <v>33</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="J14" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="K14" s="9"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="11">
         <f>ROW(B15) - ROW($B$2)</f>
@@ -2306,56 +2435,58 @@
         <v>34</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="J15" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="J16" s="9">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="K16" s="9"/>
+    </row>
+    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="11">
         <f>ROW(B17) - ROW($B$2)</f>
@@ -2368,56 +2499,58 @@
         <v>36</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="J17" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="11">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>37</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="J18" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="K18" s="9"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="11">
         <f>ROW(B19) - ROW($B$2)</f>
@@ -2430,25 +2563,26 @@
         <v>38</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="J19" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="11">
         <f t="shared" si="0"/>
@@ -2464,22 +2598,23 @@
         <v>140</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="J20" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="9"/>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="11">
         <f>ROW(B21) - ROW($B$2)</f>
@@ -2492,25 +2627,26 @@
         <v>40</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="J21" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K21" s="7"/>
+    </row>
+    <row r="22" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="11">
         <f t="shared" si="0"/>
@@ -2523,25 +2659,26 @@
         <v>41</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="J22" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K22" s="9"/>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="11">
         <f>ROW(B23) - ROW($B$2)</f>
@@ -2554,56 +2691,58 @@
         <v>42</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="J23" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="K23" s="7"/>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="J24" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K24" s="9"/>
+    </row>
+    <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="11">
         <f>ROW(B25) - ROW($B$2)</f>
@@ -2616,893 +2755,928 @@
         <v>44</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="J25" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>45</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="J26" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K26" s="9"/>
+    </row>
+    <row r="27" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="11">
         <f>ROW(B27) - ROW($B$2)</f>
         <v>25</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>46</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>289</v>
+        <v>425</v>
       </c>
       <c r="J27" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="K27" s="7"/>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>4</v>
+      <c r="C28" s="13" t="s">
+        <v>2</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>47</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>290</v>
+        <v>416</v>
       </c>
       <c r="J28" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K28" s="9"/>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
         <f>ROW(B29) - ROW($B$2)</f>
         <v>27</v>
       </c>
       <c r="C29" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J29" s="15">
         <v>4</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="J29" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="J30" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E30" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="J30" s="17">
+        <v>1</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f>ROW(B31) - ROW($B$2)</f>
         <v>29</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>5</v>
+      <c r="C31" s="13" t="s">
+        <v>2</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>50</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>293</v>
+        <v>427</v>
       </c>
       <c r="J31" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>51</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>294</v>
+        <v>428</v>
       </c>
       <c r="J32" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K32" s="9"/>
+    </row>
+    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="11">
         <f>ROW(B33) - ROW($B$2)</f>
         <v>31</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="7" t="s">
+      <c r="C33" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="J33" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E33" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J33" s="15">
+        <v>1</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>53</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>296</v>
+        <v>429</v>
       </c>
       <c r="J34" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K34" s="9"/>
+    </row>
+    <row r="35" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="11">
         <f>ROW(B35) - ROW($B$2)</f>
         <v>33</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>54</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>233</v>
+        <v>472</v>
       </c>
       <c r="J35" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="K35" s="7"/>
+    </row>
+    <row r="36" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>9</v>
+      <c r="C36" s="12" t="s">
+        <v>4</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>234</v>
+        <v>311</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>234</v>
+        <v>385</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>472</v>
       </c>
       <c r="J36" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K36" s="9"/>
+    </row>
+    <row r="37" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
         <f>ROW(B37) - ROW($B$2)</f>
         <v>35</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>56</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="J37" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K37" s="7"/>
+    </row>
+    <row r="38" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>413</v>
+        <v>386</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>472</v>
       </c>
       <c r="J38" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K38" s="9"/>
+    </row>
+    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f>ROW(B39) - ROW($B$2)</f>
         <v>37</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>58</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>414</v>
+        <v>472</v>
       </c>
       <c r="J39" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K39" s="7"/>
+    </row>
+    <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>59</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F40" s="9">
-        <v>302</v>
+        <v>173</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>252</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>300</v>
+        <v>381</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>472</v>
       </c>
       <c r="J40" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="K40" s="9"/>
+    </row>
+    <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
         <f>ROW(B41) - ROW($B$2)</f>
         <v>39</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>60</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>238</v>
+        <v>473</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="J41" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K41" s="7"/>
+    </row>
+    <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>61</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>239</v>
+        <v>175</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>473</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>239</v>
+        <v>317</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>412</v>
+        <v>389</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>472</v>
       </c>
       <c r="J42" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K42" s="9"/>
+    </row>
+    <row r="43" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
         <f>ROW(B43) - ROW($B$2)</f>
         <v>41</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>240</v>
+        <v>473</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="J43" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K43" s="7"/>
+    </row>
+    <row r="44" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>241</v>
+        <v>177</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>473</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>241</v>
+        <v>391</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>472</v>
       </c>
       <c r="J44" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K44" s="9"/>
+    </row>
+    <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
         <f>ROW(B45) - ROW($B$2)</f>
         <v>43</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>450</v>
+        <v>10</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>64</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>242</v>
+        <v>473</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>242</v>
+        <v>318</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>242</v>
+        <v>430</v>
       </c>
       <c r="J45" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K45" s="7"/>
+    </row>
+    <row r="46" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>65</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>243</v>
+        <v>179</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>473</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="J46" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K46" s="9"/>
+    </row>
+    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
         <f>ROW(B47) - ROW($B$2)</f>
         <v>45</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>66</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="J47" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K47" s="7"/>
+    </row>
+    <row r="48" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>13</v>
+      <c r="C48" s="13" t="s">
+        <v>11</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>243</v>
+        <v>181</v>
+      </c>
+      <c r="F48" s="9">
+        <v>302</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>417</v>
+        <v>472</v>
       </c>
       <c r="J48" s="9">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K48" s="9"/>
+    </row>
+    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
         <f>ROW(B49) - ROW($B$2)</f>
         <v>47</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>68</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>243</v>
+        <v>473</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="J49" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K49" s="7"/>
+    </row>
+    <row r="50" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>69</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>243</v>
+        <v>183</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>473</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>306</v>
+        <v>256</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="J50" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K50" s="9"/>
+    </row>
+    <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
         <f>ROW(B51) - ROW($B$2)</f>
         <v>49</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>70</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>243</v>
+        <v>473</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>307</v>
+        <v>257</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="J51" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K51" s="7"/>
+    </row>
+    <row r="52" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>71</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>243</v>
+        <v>185</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>473</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>308</v>
+        <v>258</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>421</v>
+        <v>472</v>
       </c>
       <c r="J52" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K52" s="9"/>
+    </row>
+    <row r="53" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
         <f>ROW(B53) - ROW($B$2)</f>
         <v>51</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>13</v>
+        <v>470</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>72</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>244</v>
+        <v>473</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>416</v>
+        <v>396</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>472</v>
       </c>
       <c r="J53" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K53" s="7"/>
+    </row>
+    <row r="54" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
         <f t="shared" si="0"/>
@@ -3515,25 +3689,26 @@
         <v>73</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="J54" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="K54" s="9"/>
+    </row>
+    <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
         <f>ROW(B55) - ROW($B$2)</f>
@@ -3542,60 +3717,64 @@
       <c r="C55" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="J55" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E55" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="H55" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J55" s="15">
+        <v>2</v>
+      </c>
+      <c r="K55" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>75</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="J56" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="K56" s="9"/>
+    </row>
+    <row r="57" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
         <f>ROW(B57) - ROW($B$2)</f>
@@ -3608,25 +3787,26 @@
         <v>76</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="J57" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="K57" s="7"/>
+    </row>
+    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
         <f t="shared" si="0"/>
@@ -3639,56 +3819,58 @@
         <v>77</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="J58" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="K58" s="9"/>
+    </row>
+    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
         <f>ROW(B59) - ROW($B$2)</f>
         <v>57</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>78</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="J59" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K59" s="7"/>
+    </row>
+    <row r="60" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
         <f t="shared" si="0"/>
@@ -3701,25 +3883,26 @@
         <v>79</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>357</v>
+        <v>397</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="J60" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K60" s="9"/>
+    </row>
+    <row r="61" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
         <f>ROW(B61) - ROW($B$2)</f>
@@ -3732,25 +3915,26 @@
         <v>80</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="J61" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="K61" s="7"/>
+    </row>
+    <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
         <f t="shared" si="0"/>
@@ -3763,25 +3947,26 @@
         <v>81</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="J62" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K62" s="9"/>
+    </row>
+    <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
         <f>ROW(B63) - ROW($B$2)</f>
@@ -3794,25 +3979,26 @@
         <v>82</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="J63" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K63" s="7"/>
+    </row>
+    <row r="64" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
         <f t="shared" si="0"/>
@@ -3825,25 +4011,26 @@
         <v>83</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="J64" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K64" s="9"/>
+    </row>
+    <row r="65" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
         <f>ROW(B65) - ROW($B$2)</f>
@@ -3856,56 +4043,58 @@
         <v>84</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="J65" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K65" s="7"/>
+    </row>
+    <row r="66" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>85</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="J66" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K66" s="9"/>
+    </row>
+    <row r="67" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f>ROW(B67) - ROW($B$2)</f>
@@ -3918,87 +4107,90 @@
         <v>86</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="J67" s="7">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K67" s="7"/>
+    </row>
+    <row r="68" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="11">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D68" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="J68" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K68" s="9"/>
+    </row>
+    <row r="69" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f>ROW(B69) - ROW($B$2)</f>
         <v>67</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>88</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="J69" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K69" s="7"/>
+    </row>
+    <row r="70" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
         <f t="shared" si="0"/>
@@ -4011,25 +4203,26 @@
         <v>89</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="J70" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K70" s="9"/>
+    </row>
+    <row r="71" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
         <f>ROW(B71) - ROW($B$2)</f>
@@ -4042,149 +4235,154 @@
         <v>90</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="J71" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K71" s="7"/>
+    </row>
+    <row r="72" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>91</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="J72" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K72" s="9"/>
+    </row>
+    <row r="73" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
         <f>ROW(B73) - ROW($B$2)</f>
         <v>71</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E73" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="I73" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="J73" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E73" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I73" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J73" s="15">
+        <v>1</v>
+      </c>
+      <c r="K73" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>13</v>
-      </c>
+      <c r="C74" s="13"/>
       <c r="D74" s="9" t="s">
         <v>93</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="J74" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K74" s="9"/>
+    </row>
+    <row r="75" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
         <f>ROW(B75) - ROW($B$2)</f>
         <v>73</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>94</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="J75" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K75" s="7"/>
+    </row>
+    <row r="76" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
         <f t="shared" si="0"/>
@@ -4197,118 +4395,126 @@
         <v>95</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="J76" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K76" s="9"/>
+    </row>
+    <row r="77" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
         <f>ROW(B77) - ROW($B$2)</f>
         <v>75</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="E77" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="I77" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="J77" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E77" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="F77" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="G77" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="H77" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I77" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J77" s="15">
+        <v>21</v>
+      </c>
+      <c r="K77" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="9" t="s">
+      <c r="C78" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E78" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="I78" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="J78" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E78" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G78" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="H78" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I78" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="J78" s="15">
+        <v>1</v>
+      </c>
+      <c r="K78" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
         <f>ROW(B79) - ROW($B$2)</f>
         <v>77</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>98</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="J79" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K79" s="7"/>
+    </row>
+    <row r="80" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f t="shared" si="0"/>
@@ -4321,707 +4527,1253 @@
         <v>99</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="J80" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K80" s="9"/>
+    </row>
+    <row r="81" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f>ROW(B81) - ROW($B$2)</f>
         <v>79</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="J81" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K81" s="7"/>
+    </row>
+    <row r="82" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="D82" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E82" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="I82" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="J82" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E82" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F82" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G82" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="H82" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I82" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J82" s="15">
+        <v>1</v>
+      </c>
+      <c r="K82" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="11">
         <f>ROW(B83) - ROW($B$2)</f>
         <v>81</v>
       </c>
-      <c r="C83" s="12" t="s">
-        <v>15</v>
+      <c r="C83" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>102</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>246</v>
+        <v>347</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>246</v>
+        <v>454</v>
       </c>
       <c r="J83" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="K83" s="7"/>
+    </row>
+    <row r="84" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>103</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>337</v>
+        <v>455</v>
       </c>
       <c r="J84" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="K84" s="9"/>
+    </row>
+    <row r="85" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
         <f>ROW(B85) - ROW($B$2)</f>
         <v>83</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>104</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>338</v>
+        <v>456</v>
       </c>
       <c r="J85" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K85" s="7"/>
+    </row>
+    <row r="86" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="C86" s="13"/>
+      <c r="C86" s="13" t="s">
+        <v>13</v>
+      </c>
       <c r="D86" s="9" t="s">
         <v>105</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>339</v>
+        <v>457</v>
       </c>
       <c r="J86" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K86" s="9"/>
+    </row>
+    <row r="87" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
         <f>ROW(B87) - ROW($B$2)</f>
         <v>85</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E87" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="I87" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="J87" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E87" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="F87" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I87" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J87" s="15">
+        <v>1</v>
+      </c>
+      <c r="K87" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>107</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>341</v>
+        <v>458</v>
       </c>
       <c r="J88" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="K88" s="9"/>
+    </row>
+    <row r="89" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
         <f>ROW(B89) - ROW($B$2)</f>
         <v>87</v>
       </c>
-      <c r="C89" s="13" t="s">
-        <v>17</v>
+      <c r="C89" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>108</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>342</v>
+        <v>437</v>
       </c>
       <c r="J89" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K89" s="7"/>
+    </row>
+    <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="C90" s="13" t="s">
-        <v>17</v>
+      <c r="C90" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>343</v>
+        <v>459</v>
       </c>
       <c r="J90" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K90" s="9"/>
+    </row>
+    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
         <f>ROW(B91) - ROW($B$2)</f>
         <v>89</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>110</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>344</v>
+        <v>435</v>
       </c>
       <c r="J91" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K91" s="7"/>
+    </row>
+    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E92" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="H92" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="I92" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="J92" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E92" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="F92" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="G92" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="H92" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I92" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J92" s="15">
+        <v>4</v>
+      </c>
+      <c r="K92" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="11">
         <f>ROW(B93) - ROW($B$2)</f>
         <v>91</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>112</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>346</v>
+        <v>460</v>
       </c>
       <c r="J93" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K93" s="7"/>
+    </row>
+    <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="11">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="C94" s="13" t="s">
-        <v>17</v>
+      <c r="C94" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="J94" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K94" s="9"/>
+    </row>
+    <row r="95" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="11">
         <f>ROW(B95) - ROW($B$2)</f>
         <v>93</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>114</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>348</v>
+        <v>462</v>
       </c>
       <c r="J95" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="K95" s="7"/>
+    </row>
+    <row r="96" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="11">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="C96" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D96" s="9" t="s">
+      <c r="C96" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="E96" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F96" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="H96" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="I96" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="J96" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E96" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="F96" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="G96" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="H96" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I96" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J96" s="15">
+        <v>1</v>
+      </c>
+      <c r="K96" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="11">
         <f>ROW(B97) - ROW($B$2)</f>
         <v>95</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D97" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E97" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="I97" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="J97" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E97" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="F97" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G97" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="H97" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I97" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="J97" s="15">
+        <v>1</v>
+      </c>
+      <c r="K97" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="11">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D98" s="9" t="s">
         <v>117</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>259</v>
+        <v>223</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>473</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>351</v>
+        <v>263</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="J98" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="K98" s="9"/>
+    </row>
+    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="11">
         <f>ROW(B99) - ROW($B$2)</f>
         <v>97</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>118</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>260</v>
+        <v>473</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="I99" s="8" t="s">
-        <v>446</v>
+        <v>400</v>
+      </c>
+      <c r="I99" s="10" t="s">
+        <v>472</v>
       </c>
       <c r="J99" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K99" s="7"/>
+    </row>
+    <row r="100" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="11">
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
-      <c r="C100" s="12" t="s">
-        <v>19</v>
+      <c r="C100" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>119</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="J100" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K100" s="9"/>
+    </row>
+    <row r="101" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="11">
         <f>ROW(B101) - ROW($B$2)</f>
         <v>99</v>
       </c>
-      <c r="C101" s="12" t="s">
-        <v>20</v>
+      <c r="C101" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>120</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="I101" s="8" t="s">
-        <v>445</v>
+        <v>402</v>
+      </c>
+      <c r="I101" s="10" t="s">
+        <v>472</v>
       </c>
       <c r="J101" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K101" s="7"/>
+    </row>
+    <row r="102" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="11">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D102" s="9" t="s">
         <v>121</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="J102" s="9">
         <v>1</v>
       </c>
+      <c r="K102" s="9"/>
+    </row>
+    <row r="103" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="1"/>
+      <c r="B103" s="11">
+        <f>ROW(B103) - ROW($B$2)</f>
+        <v>101</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="I103" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J103" s="7">
+        <v>2</v>
+      </c>
+      <c r="K103" s="7"/>
+    </row>
+    <row r="104" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1"/>
+      <c r="B104" s="11">
+        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="I104" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J104" s="9">
+        <v>1</v>
+      </c>
+      <c r="K104" s="9"/>
+    </row>
+    <row r="105" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1"/>
+      <c r="B105" s="11">
+        <f>ROW(B105) - ROW($B$2)</f>
+        <v>103</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="I105" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J105" s="7">
+        <v>1</v>
+      </c>
+      <c r="K105" s="7"/>
+    </row>
+    <row r="106" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="1"/>
+      <c r="B106" s="11">
+        <f t="shared" si="0"/>
+        <v>104</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="I106" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J106" s="9">
+        <v>1</v>
+      </c>
+      <c r="K106" s="9"/>
+    </row>
+    <row r="107" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="1"/>
+      <c r="B107" s="11">
+        <f>ROW(B107) - ROW($B$2)</f>
+        <v>105</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="I107" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J107" s="7">
+        <v>1</v>
+      </c>
+      <c r="K107" s="7"/>
+    </row>
+    <row r="108" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="1"/>
+      <c r="B108" s="11">
+        <f t="shared" si="0"/>
+        <v>106</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="I108" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J108" s="9">
+        <v>1</v>
+      </c>
+      <c r="K108" s="9"/>
+    </row>
+    <row r="109" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="1"/>
+      <c r="B109" s="11">
+        <f>ROW(B109) - ROW($B$2)</f>
+        <v>107</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="I109" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J109" s="7">
+        <v>1</v>
+      </c>
+      <c r="K109" s="7"/>
+    </row>
+    <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="1"/>
+      <c r="B110" s="11">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="I110" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J110" s="9">
+        <v>1</v>
+      </c>
+      <c r="K110" s="9"/>
+    </row>
+    <row r="111" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="1"/>
+      <c r="B111" s="11">
+        <f>ROW(B111) - ROW($B$2)</f>
+        <v>109</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="I111" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J111" s="7">
+        <v>1</v>
+      </c>
+      <c r="K111" s="7"/>
+    </row>
+    <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="1"/>
+      <c r="B112" s="11">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="I112" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J112" s="9">
+        <v>1</v>
+      </c>
+      <c r="K112" s="9"/>
+    </row>
+    <row r="113" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="1"/>
+      <c r="B113" s="11">
+        <f>ROW(B113) - ROW($B$2)</f>
+        <v>111</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="J113" s="7">
+        <v>1</v>
+      </c>
+      <c r="K113" s="7"/>
+    </row>
+    <row r="114" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="1"/>
+      <c r="B114" s="11">
+        <f t="shared" si="0"/>
+        <v>112</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="I114" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="J114" s="9">
+        <v>1</v>
+      </c>
+      <c r="K114" s="9"/>
+    </row>
+    <row r="115" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="1"/>
+      <c r="B115" s="11">
+        <f>ROW(B115) - ROW($B$2)</f>
+        <v>113</v>
+      </c>
+      <c r="C115" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="J115" s="7">
+        <v>1</v>
+      </c>
+      <c r="K115" s="7"/>
+    </row>
+    <row r="116" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="1"/>
+      <c r="B116" s="11">
+        <f t="shared" si="0"/>
+        <v>114</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="J116" s="9">
+        <v>1</v>
+      </c>
+      <c r="K116" s="9"/>
+    </row>
+    <row r="117" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="1"/>
+      <c r="B117" s="11">
+        <f>ROW(B117) - ROW($B$2)</f>
+        <v>115</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="J117" s="7">
+        <v>1</v>
+      </c>
+      <c r="K117" s="7"/>
+    </row>
+    <row r="118" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B118" s="11">
+        <f>ROW(B118) - ROW($B$2)</f>
+        <v>116</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="H118" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="J118" s="7">
+        <v>2</v>
+      </c>
+      <c r="K118" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
